--- a/archives/jira_cards.xlsx
+++ b/archives/jira_cards.xlsx
@@ -423,41 +423,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Tipo de issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Chave</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Resumo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SITUAÇÃO</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Veiculo - Marca/Modelo</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>DT. PREVISÃO ENTREGA</t>
         </is>
@@ -466,35 +471,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>TENSYLON-816</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Tensylon</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/TENSYLON-816</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>30963</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>VOLVO - EX30 ULTRA SUV - 2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -503,35 +513,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>TENSYLON-812</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Tensylon</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/TENSYLON-812</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>30948</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
@@ -540,35 +555,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>TENSYLON-801</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Tensylon</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/TENSYLON-801</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>30864</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>KIA - CARNIVAL VAN - 2025</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
@@ -577,35 +597,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>TENSYLON-761</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Tensylon</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/TENSYLON-761</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>30628</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
@@ -614,35 +639,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>TENSYLON-730</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Tensylon</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/TENSYLON-730</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>30483</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>A Produzir</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>JEEP - COMMANDER SUV - 2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
@@ -651,35 +681,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>TENSYLON-728</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Tensylon</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/TENSYLON-728</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>30472</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>A Produzir</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>🟢RECEBIDO LIBERADO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>LAND ROVER - DISCOVERY SPORT SUV - 2023</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -688,35 +723,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>TENSYLON-674</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Tensylon</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/TENSYLON-674</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>30281</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>MERCEDES-BENZ - GLS SUV - 2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -725,25 +765,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
+          <t>MANTA-30807</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30807</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>30439 PEDIDO AVULSO</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>🟢RECEBIDO LIBERADO</t>
         </is>
@@ -752,30 +797,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
+          <t>MANTA-30781</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30781</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>30911 PED AVULSO</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>A Produzir</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>🟢RECEBIDO LIBERADO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>VOLVO - XC90 - 2026</t>
         </is>
@@ -784,35 +834,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
+          <t>MANTA-30763</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30763</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>31136 - ALT</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -821,35 +876,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
+          <t>MANTA-30740</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30740</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>31140</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -858,35 +918,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
+          <t>MANTA-30739</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30739</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>31139</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -895,35 +960,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
+          <t>MANTA-30738</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30738</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>31138</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -932,35 +1002,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
+          <t>MANTA-30737</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30737</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>31137</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -969,35 +1044,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
+          <t>MANTA-30735</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30735</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>31135</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1006,35 +1086,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
+          <t>MANTA-30734</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30734</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>31134</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>A Produzir</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -1043,35 +1128,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
+          <t>MANTA-30733</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30733</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>31133</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1080,35 +1170,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
+          <t>MANTA-30732</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30732</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>31132</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1117,35 +1212,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
+          <t>MANTA-30730</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30730</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>31130</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1154,35 +1254,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
+          <t>MANTA-30720</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30720</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>30931 - ALT</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1191,35 +1296,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
+          <t>MANTA-30718</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30718</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>31120</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1228,35 +1338,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
+          <t>MANTA-30658</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30658</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>31061</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1265,35 +1380,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
+          <t>MANTA-30657</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30657</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>31060</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1302,35 +1422,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
+          <t>MANTA-30656</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30656</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>31059</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1339,35 +1464,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
+          <t>MANTA-30649</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30649</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>31054</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1376,35 +1506,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
+          <t>MANTA-30647</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30647</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>31052</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>JEEP - COMPASS SUV - 2026</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -1413,35 +1548,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
+          <t>MANTA-30638</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30638</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>31043</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -1450,35 +1590,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
+          <t>MANTA-30630</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30630</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>31036</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>GWM - HAVAL H6 GT - 2026</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -1487,35 +1632,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
+          <t>MANTA-30628</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30628</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>31034</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>GWM - HAVAL H9 SUV - 2026</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -1524,35 +1674,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
+          <t>MANTA-30624</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30624</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>31030</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1561,35 +1716,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
+          <t>MANTA-30622</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30622</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>31028</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1598,35 +1758,40 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
+          <t>MANTA-30619</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30619</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>31025</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1635,35 +1800,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
+          <t>MANTA-30615</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30615</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>31021</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1672,35 +1842,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
+          <t>MANTA-30613</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30613</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>31019</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1709,35 +1884,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
+          <t>MANTA-30610</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30610</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>31016</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1746,35 +1926,40 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
+          <t>MANTA-30609</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30609</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>31015</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1783,35 +1968,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
+          <t>MANTA-30608</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30608</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>31014</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1820,35 +2010,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
+          <t>MANTA-30607</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30607</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>31013</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1857,35 +2052,40 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
+          <t>MANTA-30606</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30606</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>31012</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1894,35 +2094,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
+          <t>MANTA-30602</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30602</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>31009</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1931,35 +2136,40 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
+          <t>MANTA-30600</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30600</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>31006</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -1968,35 +2178,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
+          <t>MANTA-30597</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30597</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>31003</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2005,35 +2220,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
+          <t>MANTA-30595</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30595</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>31001</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2042,35 +2262,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
+          <t>MANTA-30594</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30594</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>31000</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2079,35 +2304,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
+          <t>MANTA-30593</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30593</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>30999</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2116,35 +2346,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
+          <t>MANTA-30590</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30590</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>30996</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2153,35 +2388,40 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
+          <t>MANTA-30589</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30589</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>30995</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2190,35 +2430,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
+          <t>MANTA-30588</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30588</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>30994</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2227,35 +2472,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
+          <t>MANTA-30586</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30586</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>30992</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2264,35 +2514,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
+          <t>MANTA-30585</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30585</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>30991</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2301,35 +2556,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
+          <t>MANTA-30584</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30584</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>30990</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2338,35 +2598,40 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="inlineStr">
+          <t>MANTA-30583</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30583</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>30989</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2375,35 +2640,40 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
+          <t>MANTA-30582</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30582</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>30988</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2412,35 +2682,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
+          <t>MANTA-30581</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30581</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>30987</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2449,35 +2724,40 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B56" s="1" t="inlineStr">
+          <t>MANTA-30580</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30580</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>30986</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2486,35 +2766,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
+          <t>MANTA-30579</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30579</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>30985</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2523,35 +2808,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
+          <t>MANTA-30578</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30578</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>30984</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2560,35 +2850,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
+          <t>MANTA-30577</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30577</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>30983</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2597,35 +2892,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
+          <t>MANTA-30576</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30576</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>30982</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2634,35 +2934,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
+          <t>MANTA-30575</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30575</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>30981</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2671,35 +2976,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
+          <t>MANTA-30574</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30574</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>30980</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2708,35 +3018,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
+          <t>MANTA-30573</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30573</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>30979</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2745,35 +3060,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
+          <t>MANTA-30571</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30571</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>30977</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2782,35 +3102,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
+          <t>MANTA-30570</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30570</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>30976</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2819,35 +3144,40 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
+          <t>MANTA-30569</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30569</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>30975</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -2856,35 +3186,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
+          <t>MANTA-30568</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30568</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>30974</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>HONDA - WR-V - 2026</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -2893,35 +3228,40 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
+          <t>MANTA-30567</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30567</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>30973</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>HONDA - NEW HR-V SUV - 2026</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -2930,35 +3270,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
+          <t>MANTA-30542</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30542</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>30948</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -2967,35 +3312,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B70" s="1" t="inlineStr">
+          <t>MANTA-30530</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30530</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>30939</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3004,35 +3354,40 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
+          <t>MANTA-30526</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30526</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>30935</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -3041,35 +3396,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B72" s="1" t="inlineStr">
+          <t>MANTA-30525</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30525</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>30934</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -3078,35 +3438,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B73" s="1" t="inlineStr">
+          <t>MANTA-30523</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30523</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>30932</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -3115,35 +3480,40 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B74" s="1" t="inlineStr">
+          <t>MANTA-30521</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30521</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>30930</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3152,35 +3522,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
+          <t>MANTA-30515</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30515</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>30924</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3189,35 +3564,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
+          <t>MANTA-30514</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30514</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>30923</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3226,35 +3606,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
+          <t>MANTA-30513</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30513</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>30922</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3263,35 +3648,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B78" s="1" t="inlineStr">
+          <t>MANTA-30512</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>30921</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3300,35 +3690,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B79" s="1" t="inlineStr">
+          <t>MANTA-30511</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>30920</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3337,35 +3732,40 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B80" s="1" t="inlineStr">
+          <t>MANTA-30510</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30510</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>30919</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3374,35 +3774,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B81" s="1" t="inlineStr">
+          <t>MANTA-30509</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>30918</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3411,35 +3816,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B82" s="1" t="inlineStr">
+          <t>MANTA-30507</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30507</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>30916</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3448,72 +3858,82 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
+          <t>MANTA-30506</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30506</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>30915</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B84" s="1" t="inlineStr">
+          <t>MANTA-30505</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>30914</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3522,35 +3942,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B85" s="1" t="inlineStr">
+          <t>MANTA-30504</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30504</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>30913</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>JAECOO - JAECOO 7 SUV - 2026</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -3559,35 +3984,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B86" s="1" t="inlineStr">
+          <t>MANTA-30479</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30479</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>30892</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>LEXUS - NX 350 H SUV - 2026</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -3596,35 +4026,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B87" s="1" t="inlineStr">
+          <t>MANTA-30469</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30469</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>30882</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>MINI - COOPER 04 PORTAS HATCH - 2026</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -3633,72 +4068,82 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="inlineStr">
+          <t>MANTA-30464</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30464</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>30877</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B89" s="1" t="inlineStr">
+          <t>MANTA-30463</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>30876</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3707,72 +4152,82 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B90" s="1" t="inlineStr">
+          <t>MANTA-30462</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30462</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>30875</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B91" s="1" t="inlineStr">
+          <t>MANTA-30452</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>30865</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3781,35 +4236,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
+          <t>MANTA-30451</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30451</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>30864</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>KIA - CARNIVAL VAN - 2025</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -3818,35 +4278,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B93" s="1" t="inlineStr">
+          <t>MANTA-30428</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30428</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>30841</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3855,35 +4320,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
+          <t>MANTA-30421</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>30834</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3892,35 +4362,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B95" s="1" t="inlineStr">
+          <t>MANTA-30420</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>30833</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -3929,35 +4404,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="inlineStr">
+          <t>MANTA-30367</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>30786</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -3966,35 +4446,40 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="inlineStr">
+          <t>MANTA-30309</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30309</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>30735</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -4003,35 +4488,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B98" s="1" t="inlineStr">
+          <t>MANTA-30257</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>30687</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -4040,35 +4530,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B99" s="1" t="inlineStr">
+          <t>MANTA-30242</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>30674</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -4077,35 +4572,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B100" s="1" t="inlineStr">
+          <t>MANTA-30224</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>30657</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -4114,35 +4614,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
+          <t>MANTA-30196</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>30632</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
@@ -4151,35 +4656,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="inlineStr">
+          <t>MANTA-30191</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30191</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>30628</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -4188,35 +4698,40 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B103" s="1" t="inlineStr">
+          <t>MANTA-30026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30026</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>30483</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>JEEP - COMMANDER SUV - 2026</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -4225,35 +4740,40 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B104" s="1" t="inlineStr">
+          <t>MANTA-29945</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-29945</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>30412</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>GWM - HAVAL H6 HEV 2 - 2026</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -4262,35 +4782,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="inlineStr">
+          <t>MANTA-29923</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>30392</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -4299,35 +4824,40 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B106" s="1" t="inlineStr">
+          <t>MANTA-29866</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>30344</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -4336,35 +4866,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="inlineStr">
+          <t>MANTA-29791</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-29791</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>30281</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
           <t>MERCEDES-BENZ - GLS SUV - 2026</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -4373,35 +4908,40 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B108" s="1" t="inlineStr">
+          <t>MANTA-29372</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>29901</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -4410,35 +4950,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="inlineStr">
+          <t>MANTA-27100</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-27100</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>28192</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
       <c r="E109" t="inlineStr">
         <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>LEXUS - RX 500H SUV - 2025</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -4446,114 +4991,114 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
